--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/51.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/51.xlsx
@@ -426,13 +426,13 @@
         <v>-16.37984441473861</v>
       </c>
       <c r="E2">
-        <v>-11.02967563858773</v>
+        <v>-23.25547768248387</v>
       </c>
       <c r="F2">
-        <v>-4.657729469095318</v>
+        <v>-5.507011492080705</v>
       </c>
       <c r="G2">
-        <v>-8.363786574901836</v>
+        <v>-13.00841906613407</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.6964701200721</v>
       </c>
       <c r="E3">
-        <v>-11.20987267630095</v>
+        <v>-24.40499005306492</v>
       </c>
       <c r="F3">
-        <v>-4.67524446946011</v>
+        <v>-5.493662351384591</v>
       </c>
       <c r="G3">
-        <v>-7.299184650928547</v>
+        <v>-14.10527066947816</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.87180967165148</v>
       </c>
       <c r="E4">
-        <v>-11.36828775403728</v>
+        <v>-26.13709966168078</v>
       </c>
       <c r="F4">
-        <v>-4.794975037125945</v>
+        <v>-4.825543451024052</v>
       </c>
       <c r="G4">
-        <v>-6.860173206965794</v>
+        <v>-14.16235275093905</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.96010868452651</v>
       </c>
       <c r="E5">
-        <v>-12.14124392545851</v>
+        <v>-24.64244058765712</v>
       </c>
       <c r="F5">
-        <v>-4.809557616884828</v>
+        <v>-5.765753707079936</v>
       </c>
       <c r="G5">
-        <v>-7.767795682557923</v>
+        <v>-13.76206641342192</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.97587678933672</v>
       </c>
       <c r="E6">
-        <v>-12.92929802922132</v>
+        <v>-25.85210015000805</v>
       </c>
       <c r="F6">
-        <v>-4.628982635115967</v>
+        <v>-5.106625906509383</v>
       </c>
       <c r="G6">
-        <v>-6.823383114387874</v>
+        <v>-13.82643997143305</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.94507280647834</v>
       </c>
       <c r="E7">
-        <v>-13.83050058453979</v>
+        <v>-25.97070541274294</v>
       </c>
       <c r="F7">
-        <v>-4.703866219961639</v>
+        <v>-5.393867273634529</v>
       </c>
       <c r="G7">
-        <v>-6.791697883031509</v>
+        <v>-14.73183279460448</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.89679431066617</v>
       </c>
       <c r="E8">
-        <v>-13.17424771677022</v>
+        <v>-26.02581694141629</v>
       </c>
       <c r="F8">
-        <v>-4.821279844001843</v>
+        <v>-5.324075663213865</v>
       </c>
       <c r="G8">
-        <v>-6.921064071069609</v>
+        <v>-13.2535484105894</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.856322427784876</v>
       </c>
       <c r="E9">
-        <v>-14.20287700219052</v>
+        <v>-26.66227132082432</v>
       </c>
       <c r="F9">
-        <v>-4.617909019675342</v>
+        <v>-4.442368026613294</v>
       </c>
       <c r="G9">
-        <v>-7.392621488228936</v>
+        <v>-14.22145095463335</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.840664001958171</v>
       </c>
       <c r="E10">
-        <v>-14.13088785089058</v>
+        <v>-24.873211623088</v>
       </c>
       <c r="F10">
-        <v>-4.232559959199637</v>
+        <v>-4.906375542189228</v>
       </c>
       <c r="G10">
-        <v>-6.960608537536204</v>
+        <v>-14.19260451607691</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.865574684427115</v>
       </c>
       <c r="E11">
-        <v>-14.35335819346541</v>
+        <v>-27.82824016594925</v>
       </c>
       <c r="F11">
-        <v>-4.114672509005032</v>
+        <v>-5.083090331861044</v>
       </c>
       <c r="G11">
-        <v>-6.816457453119718</v>
+        <v>-13.94345451406413</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.944948377501513</v>
       </c>
       <c r="E12">
-        <v>-15.4683001934719</v>
+        <v>-28.05398912370562</v>
       </c>
       <c r="F12">
-        <v>-3.910576034833678</v>
+        <v>-4.478204857193206</v>
       </c>
       <c r="G12">
-        <v>-6.959777590605847</v>
+        <v>-14.06543984082242</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.085496364509326</v>
       </c>
       <c r="E13">
-        <v>-15.63379780455622</v>
+        <v>-27.80812921288118</v>
       </c>
       <c r="F13">
-        <v>-4.135587957558316</v>
+        <v>-4.424463693569185</v>
       </c>
       <c r="G13">
-        <v>-6.777926013588141</v>
+        <v>-14.25804241447891</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.307816992216657</v>
       </c>
       <c r="E14">
-        <v>-15.34832733158669</v>
+        <v>-26.09883405631597</v>
       </c>
       <c r="F14">
-        <v>-3.637081424757991</v>
+        <v>-4.25400721962552</v>
       </c>
       <c r="G14">
-        <v>-6.564819576134177</v>
+        <v>-13.22197904832691</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.621904314064151</v>
       </c>
       <c r="E15">
-        <v>-16.37019107683953</v>
+        <v>-27.73955453098303</v>
       </c>
       <c r="F15">
-        <v>-4.154962642742394</v>
+        <v>-4.304931105712619</v>
       </c>
       <c r="G15">
-        <v>-6.414507566469108</v>
+        <v>-12.50921859372182</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.035399100798206</v>
       </c>
       <c r="E16">
-        <v>-16.44757816915661</v>
+        <v>-28.9046674945205</v>
       </c>
       <c r="F16">
-        <v>-3.278115037694047</v>
+        <v>-3.636087383874631</v>
       </c>
       <c r="G16">
-        <v>-6.026157400893823</v>
+        <v>-13.45123763746698</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.552216464698173</v>
       </c>
       <c r="E17">
-        <v>-16.87738016569861</v>
+        <v>-28.75131977919876</v>
       </c>
       <c r="F17">
-        <v>-3.032417952554103</v>
+        <v>-3.925450199918346</v>
       </c>
       <c r="G17">
-        <v>-5.15225945271025</v>
+        <v>-14.35310638491185</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.174698050905797</v>
       </c>
       <c r="E18">
-        <v>-17.94891674234158</v>
+        <v>-29.53839346833891</v>
       </c>
       <c r="F18">
-        <v>-3.007275345144332</v>
+        <v>-3.879851887863845</v>
       </c>
       <c r="G18">
-        <v>-4.873557865941166</v>
+        <v>-12.9926410060939</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.898065970232515</v>
       </c>
       <c r="E19">
-        <v>-17.60808114615428</v>
+        <v>-29.65819198397483</v>
       </c>
       <c r="F19">
-        <v>-2.590059819050333</v>
+        <v>-3.355441478010575</v>
       </c>
       <c r="G19">
-        <v>-5.27849055412266</v>
+        <v>-12.04001828498646</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.722321266607451</v>
       </c>
       <c r="E20">
-        <v>-19.70452913105725</v>
+        <v>-28.49118158982814</v>
       </c>
       <c r="F20">
-        <v>-2.438779222114074</v>
+        <v>-3.314245938701953</v>
       </c>
       <c r="G20">
-        <v>-5.39455165963843</v>
+        <v>-12.4173807499169</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.638183770129719</v>
       </c>
       <c r="E21">
-        <v>-19.88779194567367</v>
+        <v>-30.12509350382467</v>
       </c>
       <c r="F21">
-        <v>-2.087317843719493</v>
+        <v>-3.230532785709841</v>
       </c>
       <c r="G21">
-        <v>-5.158794469604771</v>
+        <v>-12.687948326296</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.633373952407193</v>
       </c>
       <c r="E22">
-        <v>-18.63892938383833</v>
+        <v>-30.08587918315525</v>
       </c>
       <c r="F22">
-        <v>-2.185485179523055</v>
+        <v>-2.870356153870408</v>
       </c>
       <c r="G22">
-        <v>-5.237794017808399</v>
+        <v>-13.08214822583917</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.693874766059945</v>
       </c>
       <c r="E23">
-        <v>-20.00598964574787</v>
+        <v>-28.9920444004985</v>
       </c>
       <c r="F23">
-        <v>-1.662804400806831</v>
+        <v>-2.992595846399322</v>
       </c>
       <c r="G23">
-        <v>-5.250092694486792</v>
+        <v>-13.00229786743195</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.80719986172762</v>
       </c>
       <c r="E24">
-        <v>-19.67372645085708</v>
+        <v>-29.33047084851373</v>
       </c>
       <c r="F24">
-        <v>-1.857836878856752</v>
+        <v>-2.422331158964087</v>
       </c>
       <c r="G24">
-        <v>-5.523957574223001</v>
+        <v>-13.54601027989247</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.959425028720213</v>
       </c>
       <c r="E25">
-        <v>-20.8964280183501</v>
+        <v>-31.03639229194323</v>
       </c>
       <c r="F25">
-        <v>-2.010854562236682</v>
+        <v>-2.74959509715549</v>
       </c>
       <c r="G25">
-        <v>-6.3014358835753</v>
+        <v>-13.29176865884029</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.140141844845364</v>
       </c>
       <c r="E26">
-        <v>-19.23663361116273</v>
+        <v>-28.78229454141123</v>
       </c>
       <c r="F26">
-        <v>-1.742372403315335</v>
+        <v>-3.302434247905435</v>
       </c>
       <c r="G26">
-        <v>-6.514932965402899</v>
+        <v>-13.11440618157383</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.336613041091589</v>
       </c>
       <c r="E27">
-        <v>-20.02381371944206</v>
+        <v>-29.13027606958264</v>
       </c>
       <c r="F27">
-        <v>-1.801417603419481</v>
+        <v>-2.942153241773249</v>
       </c>
       <c r="G27">
-        <v>-5.546489147163281</v>
+        <v>-13.26371840648604</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.536097998084839</v>
       </c>
       <c r="E28">
-        <v>-20.07023057802068</v>
+        <v>-27.45582752050645</v>
       </c>
       <c r="F28">
-        <v>-1.8985370544585</v>
+        <v>-3.000556457140225</v>
       </c>
       <c r="G28">
-        <v>-5.985066909660389</v>
+        <v>-13.57060597797648</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.727008875905165</v>
       </c>
       <c r="E29">
-        <v>-19.96441372588345</v>
+        <v>-29.88659009902569</v>
       </c>
       <c r="F29">
-        <v>-1.968317896102928</v>
+        <v>-2.718890002635921</v>
       </c>
       <c r="G29">
-        <v>-6.48948811238806</v>
+        <v>-13.41007431423168</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.902500402142403</v>
       </c>
       <c r="E30">
-        <v>-19.09496935878078</v>
+        <v>-30.1209227792636</v>
       </c>
       <c r="F30">
-        <v>-2.256603006155601</v>
+        <v>-3.086787018669446</v>
       </c>
       <c r="G30">
-        <v>-5.790317447221682</v>
+        <v>-13.63510864726364</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.056454940867559</v>
       </c>
       <c r="E31">
-        <v>-18.57288159043646</v>
+        <v>-29.39399628189333</v>
       </c>
       <c r="F31">
-        <v>-1.91006213013365</v>
+        <v>-3.241684267686328</v>
       </c>
       <c r="G31">
-        <v>-6.138292199400015</v>
+        <v>-14.84879436850693</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.186147581609585</v>
       </c>
       <c r="E32">
-        <v>-18.91483571970366</v>
+        <v>-29.14641102247197</v>
       </c>
       <c r="F32">
-        <v>-2.209987458930461</v>
+        <v>-3.00577765688007</v>
       </c>
       <c r="G32">
-        <v>-6.400828392300839</v>
+        <v>-15.15464077342527</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.288622530527432</v>
       </c>
       <c r="E33">
-        <v>-17.53346095145588</v>
+        <v>-28.23229778775764</v>
       </c>
       <c r="F33">
-        <v>-1.548935360883205</v>
+        <v>-3.314237655027926</v>
       </c>
       <c r="G33">
-        <v>-7.094923991155515</v>
+        <v>-14.10949327031351</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.361326373181484</v>
       </c>
       <c r="E34">
-        <v>-17.65188960370448</v>
+        <v>-27.8039494313721</v>
       </c>
       <c r="F34">
-        <v>-2.096611297611501</v>
+        <v>-3.340944220094181</v>
       </c>
       <c r="G34">
-        <v>-6.016920978839256</v>
+        <v>-14.14502866613204</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.403187874405293</v>
       </c>
       <c r="E35">
-        <v>-17.58244545479685</v>
+        <v>-28.21392124023451</v>
       </c>
       <c r="F35">
-        <v>-2.459977143951713</v>
+        <v>-3.359826855040996</v>
       </c>
       <c r="G35">
-        <v>-6.276431333117185</v>
+        <v>-14.61216816026921</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.416064555683911</v>
       </c>
       <c r="E36">
-        <v>-17.12942144354352</v>
+        <v>-29.82491454727823</v>
       </c>
       <c r="F36">
-        <v>-2.086173039968825</v>
+        <v>-2.841115612918988</v>
       </c>
       <c r="G36">
-        <v>-6.05700837477429</v>
+        <v>-13.91321102529012</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.401974248109275</v>
       </c>
       <c r="E37">
-        <v>-17.33744595403387</v>
+        <v>-28.15293628077322</v>
       </c>
       <c r="F37">
-        <v>-2.406335384416028</v>
+        <v>-3.52077864140494</v>
       </c>
       <c r="G37">
-        <v>-6.051430105540619</v>
+        <v>-13.55953716896593</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.365702881123479</v>
       </c>
       <c r="E38">
-        <v>-16.85697486182005</v>
+        <v>-26.78161472482246</v>
       </c>
       <c r="F38">
-        <v>-2.066687353552772</v>
+        <v>-3.473812694768417</v>
       </c>
       <c r="G38">
-        <v>-4.818248581616562</v>
+        <v>-15.22081692348253</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.311201922364401</v>
       </c>
       <c r="E39">
-        <v>-16.98143091297285</v>
+        <v>-26.64705111968454</v>
       </c>
       <c r="F39">
-        <v>-2.353280109001525</v>
+        <v>-2.897432999165715</v>
       </c>
       <c r="G39">
-        <v>-5.845328782447751</v>
+        <v>-14.11189341582948</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.241818474396521</v>
       </c>
       <c r="E40">
-        <v>-17.93360597172165</v>
+        <v>-26.59432609681323</v>
       </c>
       <c r="F40">
-        <v>-2.414357294344738</v>
+        <v>-2.550256765345817</v>
       </c>
       <c r="G40">
-        <v>-5.49198763595026</v>
+        <v>-14.3226526764961</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.161212517318094</v>
       </c>
       <c r="E41">
-        <v>-16.32245643232468</v>
+        <v>-26.15856010000313</v>
       </c>
       <c r="F41">
-        <v>-2.387956396850115</v>
+        <v>-3.309408273069604</v>
       </c>
       <c r="G41">
-        <v>-4.642226875293513</v>
+        <v>-14.12613538273942</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.07390638637082</v>
       </c>
       <c r="E42">
-        <v>-16.06587309505007</v>
+        <v>-28.23761421624264</v>
       </c>
       <c r="F42">
-        <v>-2.068697801239366</v>
+        <v>-3.626729317325205</v>
       </c>
       <c r="G42">
-        <v>-4.814405038245468</v>
+        <v>-13.20490987552643</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.983939354050908</v>
       </c>
       <c r="E43">
-        <v>-14.96122431646301</v>
+        <v>-27.69208706643463</v>
       </c>
       <c r="F43">
-        <v>-2.51822959645138</v>
+        <v>-3.496232458525185</v>
       </c>
       <c r="G43">
-        <v>-4.846249175787718</v>
+        <v>-12.44974464310882</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.896431361353496</v>
       </c>
       <c r="E44">
-        <v>-15.66704133224653</v>
+        <v>-26.4635347105237</v>
       </c>
       <c r="F44">
-        <v>-2.583518201670425</v>
+        <v>-3.700062198392837</v>
       </c>
       <c r="G44">
-        <v>-5.088816157995657</v>
+        <v>-13.31015211821986</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.814578035347536</v>
       </c>
       <c r="E45">
-        <v>-15.12095265166156</v>
+        <v>-25.57479904414835</v>
       </c>
       <c r="F45">
-        <v>-2.70147026452245</v>
+        <v>-3.861327936002442</v>
       </c>
       <c r="G45">
-        <v>-5.289762961683879</v>
+        <v>-12.87345474558906</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.739811303704699</v>
       </c>
       <c r="E46">
-        <v>-14.79249790341122</v>
+        <v>-27.27421759890284</v>
       </c>
       <c r="F46">
-        <v>-2.618188690947196</v>
+        <v>-3.528529675192935</v>
       </c>
       <c r="G46">
-        <v>-4.877682805683098</v>
+        <v>-13.34517106893427</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.673635277353954</v>
       </c>
       <c r="E47">
-        <v>-14.72220692986416</v>
+        <v>-26.62223961059651</v>
       </c>
       <c r="F47">
-        <v>-3.104218353926556</v>
+        <v>-3.425041735561193</v>
       </c>
       <c r="G47">
-        <v>-4.927334367681087</v>
+        <v>-13.61527516893787</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.617401573911847</v>
       </c>
       <c r="E48">
-        <v>-14.56721990695165</v>
+        <v>-26.01397951036024</v>
       </c>
       <c r="F48">
-        <v>-2.81950102227774</v>
+        <v>-3.728176159676449</v>
       </c>
       <c r="G48">
-        <v>-4.634483509277158</v>
+        <v>-12.0463612902397</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.572214340385117</v>
       </c>
       <c r="E49">
-        <v>-13.59955746709661</v>
+        <v>-26.92859540568942</v>
       </c>
       <c r="F49">
-        <v>-2.80876289563525</v>
+        <v>-3.892166397673862</v>
       </c>
       <c r="G49">
-        <v>-4.880900655947269</v>
+        <v>-12.56615004536067</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.540004546396244</v>
       </c>
       <c r="E50">
-        <v>-13.42383003322897</v>
+        <v>-26.40653027971515</v>
       </c>
       <c r="F50">
-        <v>-3.4345124600774</v>
+        <v>-3.924909276004318</v>
       </c>
       <c r="G50">
-        <v>-3.957291555946001</v>
+        <v>-11.69750593294792</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.520532100211738</v>
       </c>
       <c r="E51">
-        <v>-13.67512411286261</v>
+        <v>-26.22260630789361</v>
       </c>
       <c r="F51">
-        <v>-3.602051424028405</v>
+        <v>-3.854182438785894</v>
       </c>
       <c r="G51">
-        <v>-5.416921015847285</v>
+        <v>-12.48710083897395</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.511630265954205</v>
       </c>
       <c r="E52">
-        <v>-14.35290081759063</v>
+        <v>-24.76629888024091</v>
       </c>
       <c r="F52">
-        <v>-3.256497961950592</v>
+        <v>-4.427301680291176</v>
       </c>
       <c r="G52">
-        <v>-4.673733337190757</v>
+        <v>-13.05119131450145</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.510721115174682</v>
       </c>
       <c r="E53">
-        <v>-14.69562478743914</v>
+        <v>-24.86602040636382</v>
       </c>
       <c r="F53">
-        <v>-3.459973988937248</v>
+        <v>-3.98676429833876</v>
       </c>
       <c r="G53">
-        <v>-5.205178523155499</v>
+        <v>-12.15300720424178</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.514648440199257</v>
       </c>
       <c r="E54">
-        <v>-14.54762972839446</v>
+        <v>-24.98861072622546</v>
       </c>
       <c r="F54">
-        <v>-3.359279304187746</v>
+        <v>-3.662221547065553</v>
       </c>
       <c r="G54">
-        <v>-4.621913367864545</v>
+        <v>-11.8222340466855</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.519805552877172</v>
       </c>
       <c r="E55">
-        <v>-13.11834370514553</v>
+        <v>-27.72389959633851</v>
       </c>
       <c r="F55">
-        <v>-3.372958135110174</v>
+        <v>-4.022235818894037</v>
       </c>
       <c r="G55">
-        <v>-5.227885555009361</v>
+        <v>-13.60384385519076</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.523685809881116</v>
       </c>
       <c r="E56">
-        <v>-13.95391055819682</v>
+        <v>-25.99981444366425</v>
       </c>
       <c r="F56">
-        <v>-3.284078454626801</v>
+        <v>-4.067233564581509</v>
       </c>
       <c r="G56">
-        <v>-5.454743998633458</v>
+        <v>-12.51924292561474</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.52295187053736</v>
       </c>
       <c r="E57">
-        <v>-12.27151906571117</v>
+        <v>-26.34468491019239</v>
       </c>
       <c r="F57">
-        <v>-3.119196893303976</v>
+        <v>-4.207774378140473</v>
       </c>
       <c r="G57">
-        <v>-5.006019414058485</v>
+        <v>-12.47828816674841</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.513949184975808</v>
       </c>
       <c r="E58">
-        <v>-13.37857699247031</v>
+        <v>-25.60761689528194</v>
       </c>
       <c r="F58">
-        <v>-3.619878718904054</v>
+        <v>-4.574102466313096</v>
       </c>
       <c r="G58">
-        <v>-5.389162091500496</v>
+        <v>-12.07836433396784</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.494838144617101</v>
       </c>
       <c r="E59">
-        <v>-13.64782194307036</v>
+        <v>-25.46751043795863</v>
       </c>
       <c r="F59">
-        <v>-3.436191560802874</v>
+        <v>-4.628642176113416</v>
       </c>
       <c r="G59">
-        <v>-5.151074277407191</v>
+        <v>-12.46300999908468</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.464030187603623</v>
       </c>
       <c r="E60">
-        <v>-12.40382296231927</v>
+        <v>-27.34142015317667</v>
       </c>
       <c r="F60">
-        <v>-3.674951068944373</v>
+        <v>-4.223703883296309</v>
       </c>
       <c r="G60">
-        <v>-5.272650751791386</v>
+        <v>-13.35010378178778</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.421286151052897</v>
       </c>
       <c r="E61">
-        <v>-13.56801211715918</v>
+        <v>-25.4368526689267</v>
       </c>
       <c r="F61">
-        <v>-3.635487645875005</v>
+        <v>-3.900407824964314</v>
       </c>
       <c r="G61">
-        <v>-5.369649736092032</v>
+        <v>-12.22490563226367</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.367729538442831</v>
       </c>
       <c r="E62">
-        <v>-12.64466532394321</v>
+        <v>-26.76237323876387</v>
       </c>
       <c r="F62">
-        <v>-3.894008686777688</v>
+        <v>-4.454939330318179</v>
       </c>
       <c r="G62">
-        <v>-5.281609088020653</v>
+        <v>-13.00311557218015</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.304111190225272</v>
       </c>
       <c r="E63">
-        <v>-13.02261629309739</v>
+        <v>-26.36811523470807</v>
       </c>
       <c r="F63">
-        <v>-3.78421935631285</v>
+        <v>-4.754566446849982</v>
       </c>
       <c r="G63">
-        <v>-5.002331466327736</v>
+        <v>-11.94900145647527</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.23122880443823</v>
       </c>
       <c r="E64">
-        <v>-13.57295721077556</v>
+        <v>-26.37240822806735</v>
       </c>
       <c r="F64">
-        <v>-3.681466178567391</v>
+        <v>-4.514125352880801</v>
       </c>
       <c r="G64">
-        <v>-4.863172684584472</v>
+        <v>-13.55530629176674</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.152330618692644</v>
       </c>
       <c r="E65">
-        <v>-14.2432483479689</v>
+        <v>-27.50441351813474</v>
       </c>
       <c r="F65">
-        <v>-3.424390638782592</v>
+        <v>-4.872792699312334</v>
       </c>
       <c r="G65">
-        <v>-5.934643990551749</v>
+        <v>-13.72795124163973</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.071328694644017</v>
       </c>
       <c r="E66">
-        <v>-13.23343940052448</v>
+        <v>-26.29906959151313</v>
       </c>
       <c r="F66">
-        <v>-3.637771454804523</v>
+        <v>-4.777218981846937</v>
       </c>
       <c r="G66">
-        <v>-5.756814726364258</v>
+        <v>-12.74810424929009</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.994248210091379</v>
       </c>
       <c r="E67">
-        <v>-12.63304978811354</v>
+        <v>-27.25114049535975</v>
       </c>
       <c r="F67">
-        <v>-3.494004978579057</v>
+        <v>-4.656412364924866</v>
       </c>
       <c r="G67">
-        <v>-5.942913733308848</v>
+        <v>-13.80710473021094</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.927678147692174</v>
       </c>
       <c r="E68">
-        <v>-12.85078787535034</v>
+        <v>-26.57781075210726</v>
       </c>
       <c r="F68">
-        <v>-3.686880387912089</v>
+        <v>-4.511371031266492</v>
       </c>
       <c r="G68">
-        <v>-5.314270930311103</v>
+        <v>-13.68287816412255</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.87705412847808</v>
       </c>
       <c r="E69">
-        <v>-13.22913282174319</v>
+        <v>-27.6466664721377</v>
       </c>
       <c r="F69">
-        <v>-3.726796099583385</v>
+        <v>-4.602330742298295</v>
       </c>
       <c r="G69">
-        <v>-6.139742218346217</v>
+        <v>-12.79924555678075</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.845300642435685</v>
       </c>
       <c r="E70">
-        <v>-13.7643259938657</v>
+        <v>-26.82883312330044</v>
       </c>
       <c r="F70">
-        <v>-3.588588796998108</v>
+        <v>-4.36367892191916</v>
       </c>
       <c r="G70">
-        <v>-5.756688925633766</v>
+        <v>-12.26852869083465</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.835960412013065</v>
       </c>
       <c r="E71">
-        <v>-14.17430233120212</v>
+        <v>-26.71624167404773</v>
       </c>
       <c r="F71">
-        <v>-3.686970679958994</v>
+        <v>-5.030653846896432</v>
       </c>
       <c r="G71">
-        <v>-5.551610561112533</v>
+        <v>-13.03529407482187</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.850220022180175</v>
       </c>
       <c r="E72">
-        <v>-14.42463637434614</v>
+        <v>-28.64082501341161</v>
       </c>
       <c r="F72">
-        <v>-3.554233087334401</v>
+        <v>-4.217342021642808</v>
       </c>
       <c r="G72">
-        <v>-5.675808987563831</v>
+        <v>-13.06851539930845</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.88869747642559</v>
       </c>
       <c r="E73">
-        <v>-14.5268712035433</v>
+        <v>-26.3910383701349</v>
       </c>
       <c r="F73">
-        <v>-3.921114524932094</v>
+        <v>-5.10836464968786</v>
       </c>
       <c r="G73">
-        <v>-6.029941354445209</v>
+        <v>-12.14064893774368</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.94967871403147</v>
       </c>
       <c r="E74">
-        <v>-15.19449506954613</v>
+        <v>-28.41383978225114</v>
       </c>
       <c r="F74">
-        <v>-3.942671958222548</v>
+        <v>-4.626046901040445</v>
       </c>
       <c r="G74">
-        <v>-5.177227587167433</v>
+        <v>-12.22551808318844</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.028300378846134</v>
       </c>
       <c r="E75">
-        <v>-14.01785261118513</v>
+        <v>-27.17209598155586</v>
       </c>
       <c r="F75">
-        <v>-4.085850293592026</v>
+        <v>-4.691642002198527</v>
       </c>
       <c r="G75">
-        <v>-5.968100363771623</v>
+        <v>-12.93789782505651</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.116363493497821</v>
       </c>
       <c r="E76">
-        <v>-14.51578549917253</v>
+        <v>-29.62587679345609</v>
       </c>
       <c r="F76">
-        <v>-4.157432005970139</v>
+        <v>-4.427449129688875</v>
       </c>
       <c r="G76">
-        <v>-5.156635993913167</v>
+        <v>-12.30340859863641</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.206702865653319</v>
       </c>
       <c r="E77">
-        <v>-14.55539606131762</v>
+        <v>-27.72158554612059</v>
       </c>
       <c r="F77">
-        <v>-4.135307141008767</v>
+        <v>-4.813000311810862</v>
       </c>
       <c r="G77">
-        <v>-5.048258664594045</v>
+        <v>-13.55062352510144</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.291022803137099</v>
       </c>
       <c r="E78">
-        <v>-14.79545499693823</v>
+        <v>-29.23209880764511</v>
       </c>
       <c r="F78">
-        <v>-4.227653539072856</v>
+        <v>-4.969927889332006</v>
       </c>
       <c r="G78">
-        <v>-5.548094761749828</v>
+        <v>-13.67581842576006</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.362803154111906</v>
       </c>
       <c r="E79">
-        <v>-16.39392480911373</v>
+        <v>-27.33535199800639</v>
       </c>
       <c r="F79">
-        <v>-4.021705663756246</v>
+        <v>-4.463049047191586</v>
       </c>
       <c r="G79">
-        <v>-5.709894364436167</v>
+        <v>-13.01583468814203</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.416582270572145</v>
       </c>
       <c r="E80">
-        <v>-16.65262747222392</v>
+        <v>-28.16607791234348</v>
       </c>
       <c r="F80">
-        <v>-4.295389969967174</v>
+        <v>-4.811075185966756</v>
       </c>
       <c r="G80">
-        <v>-5.102240420157401</v>
+        <v>-13.37606176936121</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.447989919512906</v>
       </c>
       <c r="E81">
-        <v>-16.79030213900512</v>
+        <v>-28.86987522871957</v>
       </c>
       <c r="F81">
-        <v>-4.041151588536964</v>
+        <v>-5.712485541242914</v>
       </c>
       <c r="G81">
-        <v>-5.243302765585747</v>
+        <v>-13.28271431679038</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.453315965148092</v>
       </c>
       <c r="E82">
-        <v>-17.27575908110139</v>
+        <v>-30.53264937180399</v>
       </c>
       <c r="F82">
-        <v>-3.990505205529803</v>
+        <v>-4.870333276493422</v>
       </c>
       <c r="G82">
-        <v>-5.122318878853081</v>
+        <v>-12.90620597260907</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.433050097789927</v>
       </c>
       <c r="E83">
-        <v>-18.34857268741452</v>
+        <v>-30.77697186570283</v>
       </c>
       <c r="F83">
-        <v>-4.467522231166703</v>
+        <v>-5.174525525782053</v>
       </c>
       <c r="G83">
-        <v>-5.352193229463455</v>
+        <v>-12.27194186328564</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.388265068104016</v>
       </c>
       <c r="E84">
-        <v>-18.77508701182696</v>
+        <v>-30.77109617067787</v>
       </c>
       <c r="F84">
-        <v>-4.456896762490994</v>
+        <v>-4.88276044427022</v>
       </c>
       <c r="G84">
-        <v>-5.043617279747988</v>
+        <v>-12.9674775494499</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.323503200418169</v>
       </c>
       <c r="E85">
-        <v>-19.84092676816828</v>
+        <v>-31.57891706348417</v>
       </c>
       <c r="F85">
-        <v>-4.496578874554702</v>
+        <v>-5.434417514736371</v>
       </c>
       <c r="G85">
-        <v>-5.406413344305638</v>
+        <v>-12.92331487195602</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.24409891837578</v>
       </c>
       <c r="E86">
-        <v>-21.33706665319245</v>
+        <v>-32.60189028486888</v>
       </c>
       <c r="F86">
-        <v>-4.528877747957258</v>
+        <v>-5.874681535445863</v>
       </c>
       <c r="G86">
-        <v>-4.93154538160704</v>
+        <v>-13.11801798675718</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.156107337755525</v>
       </c>
       <c r="E87">
-        <v>-22.23479586894704</v>
+        <v>-32.54904072896237</v>
       </c>
       <c r="F87">
-        <v>-4.829266134132234</v>
+        <v>-5.673094186137589</v>
       </c>
       <c r="G87">
-        <v>-5.014689732825836</v>
+        <v>-13.1271749557188</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.064508448583481</v>
       </c>
       <c r="E88">
-        <v>-23.96883913596417</v>
+        <v>-35.22548434358274</v>
       </c>
       <c r="F88">
-        <v>-4.711490513537005</v>
+        <v>-5.420244976841873</v>
       </c>
       <c r="G88">
-        <v>-5.181392253455837</v>
+        <v>-13.0051515576868</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.977312193605291</v>
       </c>
       <c r="E89">
-        <v>-24.30123365660118</v>
+        <v>-35.01817080351159</v>
       </c>
       <c r="F89">
-        <v>-4.940568891841986</v>
+        <v>-5.987996397577016</v>
       </c>
       <c r="G89">
-        <v>-5.604506457739008</v>
+        <v>-13.03993877021347</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.900897550745769</v>
       </c>
       <c r="E90">
-        <v>-25.50885540564866</v>
+        <v>-35.22509263058108</v>
       </c>
       <c r="F90">
-        <v>-4.992128964094436</v>
+        <v>-6.190282888973252</v>
       </c>
       <c r="G90">
-        <v>-5.487481983471311</v>
+        <v>-13.31337658957511</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.843552130963668</v>
       </c>
       <c r="E91">
-        <v>-26.5535109605821</v>
+        <v>-36.29501933471433</v>
       </c>
       <c r="F91">
-        <v>-5.155907968404135</v>
+        <v>-6.192494629938727</v>
       </c>
       <c r="G91">
-        <v>-5.734932020349675</v>
+        <v>-13.06737657164295</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.812030805477531</v>
       </c>
       <c r="E92">
-        <v>-27.64750876830312</v>
+        <v>-40.36390304382023</v>
       </c>
       <c r="F92">
-        <v>-5.526019210505343</v>
+        <v>-5.749682551098223</v>
       </c>
       <c r="G92">
-        <v>-5.401460768178889</v>
+        <v>-14.20287382833973</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.81188184601632</v>
       </c>
       <c r="E93">
-        <v>-29.75250424789558</v>
+        <v>-39.43221706571914</v>
       </c>
       <c r="F93">
-        <v>-5.302815613821016</v>
+        <v>-6.283432803418057</v>
       </c>
       <c r="G93">
-        <v>-6.091444669473789</v>
+        <v>-13.48908379407193</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.84540365357652</v>
       </c>
       <c r="E94">
-        <v>-31.57875630265689</v>
+        <v>-38.50270928361573</v>
       </c>
       <c r="F94">
-        <v>-5.765800095654493</v>
+        <v>-6.413444238920036</v>
       </c>
       <c r="G94">
-        <v>-6.211018263806725</v>
+        <v>-13.25352523677063</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.917578874654766</v>
       </c>
       <c r="E95">
-        <v>-34.15963100181939</v>
+        <v>-42.40318130861337</v>
       </c>
       <c r="F95">
-        <v>-6.121684955980022</v>
+        <v>-6.412456824975899</v>
       </c>
       <c r="G95">
-        <v>-5.906898308387117</v>
+        <v>-13.35388773533917</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.0341126342243</v>
       </c>
       <c r="E96">
-        <v>-35.40885584157534</v>
+        <v>-44.75955917308262</v>
       </c>
       <c r="F96">
-        <v>-6.108947978794577</v>
+        <v>-6.573609904618723</v>
       </c>
       <c r="G96">
-        <v>-5.823979074264992</v>
+        <v>-14.43297991713785</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.195049369468581</v>
       </c>
       <c r="E97">
-        <v>-38.51649169425807</v>
+        <v>-45.85456909474436</v>
       </c>
       <c r="F97">
-        <v>-6.253911031733386</v>
+        <v>-6.609715954604545</v>
       </c>
       <c r="G97">
-        <v>-7.231891191751782</v>
+        <v>-14.33633681648267</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.410872541313307</v>
       </c>
       <c r="E98">
-        <v>-40.01501808508429</v>
+        <v>-46.66427836121184</v>
       </c>
       <c r="F98">
-        <v>-6.261667864093201</v>
+        <v>-6.515341298954702</v>
       </c>
       <c r="G98">
-        <v>-7.581402037060337</v>
+        <v>-13.67248139585647</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.669018349709528</v>
       </c>
       <c r="E99">
-        <v>-42.50324247028686</v>
+        <v>-47.61116642655669</v>
       </c>
       <c r="F99">
-        <v>-6.596856379043486</v>
+        <v>-6.651087107802561</v>
       </c>
       <c r="G99">
-        <v>-7.206654903105917</v>
+        <v>-14.67201123670985</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.986378933732992</v>
       </c>
       <c r="E100">
-        <v>-44.24626117278719</v>
+        <v>-50.1580979487947</v>
       </c>
       <c r="F100">
-        <v>-6.63869141798707</v>
+        <v>-8.009922357088307</v>
       </c>
       <c r="G100">
-        <v>-7.429977684094073</v>
+        <v>-15.2286794691383</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.329578792405356</v>
       </c>
       <c r="E101">
-        <v>-46.01159393096032</v>
+        <v>-51.17896316552884</v>
       </c>
       <c r="F101">
-        <v>-7.154746500032001</v>
+        <v>-7.66749266848645</v>
       </c>
       <c r="G101">
-        <v>-7.780316165787446</v>
+        <v>-14.76872882463966</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.747478638085533</v>
       </c>
       <c r="E102">
-        <v>-49.32307904109834</v>
+        <v>-53.74846347010258</v>
       </c>
       <c r="F102">
-        <v>-7.243896228288687</v>
+        <v>-7.945857664706898</v>
       </c>
       <c r="G102">
-        <v>-8.226183749562029</v>
+        <v>-15.15728093349284</v>
       </c>
     </row>
   </sheetData>
